--- a/branches/cpg-antimicrobiology/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/cpg-antimicrobiology/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:b273821e-88ee-400b-b05c-40c3b1f7d7cf</t>
+    <t>urn:uuid:5dabd7ea-0d0e-442c-83b5-3b690a65a014</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/cpg-antimicrobiology/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/cpg-antimicrobiology/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:5dabd7ea-0d0e-442c-83b5-3b690a65a014</t>
+    <t>urn:uuid:9d37c634-a224-4647-86ed-8402b5a23610</t>
   </si>
   <si>
     <t>Version</t>
